--- a/studies/m value study.xlsx
+++ b/studies/m value study.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hrxu/Documents/ih-project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hrxu/Documents/ih-project/studies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9678A400-2785-BD44-99FE-E4E7CB60128E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B0DB64-0EE4-EF44-A2D6-4A3B50597353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16880" xr2:uid="{85A47CF0-5B27-9E4A-B4FD-8FECB992F443}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>Magnitude (%)</t>
-  </si>
-  <si>
-    <t>Angle (deg)</t>
   </si>
   <si>
     <t>F1</t>
@@ -81,6 +78,9 @@
   </si>
   <si>
     <t>true = 32</t>
+  </si>
+  <si>
+    <t>Angle (%)</t>
   </si>
 </sst>
 </file>
@@ -170,7 +170,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -216,36 +216,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -276,7 +253,6 @@
     <xf numFmtId="11" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="11" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -284,75 +260,49 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -679,16 +629,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>10.3404941946124</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>7.5705944386300699</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.34143690664391402</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.8215009227073198</c:v>
+                  <c:v>2.8723594985034446</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.1029428996194639</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.4843585178865E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.6170835896409224</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -766,16 +716,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>10.44759412088</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.5559626046150203</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.18639265678729799</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.3575120040090303</c:v>
+                  <c:v>2.9021094780222221</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5433229457263946</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.1775737996471671E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.4881977788913974</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1021,16 +971,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>10.5078106269934</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>19.0731910385202</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.30237016814676199</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>9.6702242405897199</c:v>
+                  <c:v>2.9188362852759444</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.2981086218111662</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.3991713374100552E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.6861734001638111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1108,16 +1058,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>10.4891174175008</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.7603419265328597</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.12753018345964701</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4.83835550680742</c:v>
+                  <c:v>2.9136437270835556</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.6000949795924611</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.542505096101306E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3439876407798388</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1647,16 +1597,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>45.355199088398699</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>50.584452310884402</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.2044600007555699E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>95.340692448022693</c:v>
+                  <c:v>12.598666413444082</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14.051236753023444</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.9012777798765826E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>26.483525680006302</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1734,16 +1684,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>44.615174853890998</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>20.1586062443568</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.3091910388783402E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>24.848705492333298</c:v>
+                  <c:v>12.393104126080832</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5996128456546668</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.4144195524398337E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.9024181923148049</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1989,16 +1939,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>43.985608516044401</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>38.653362881352599</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.4304893485778803E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6.5130388260926697</c:v>
+                  <c:v>12.218224587790111</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.737045244820166</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.064024819049411E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.8091774516924082</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2076,16 +2026,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>44.503220697609102</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>25.969377031096201</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.8963469128291799E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>19.032728305550702</c:v>
+                  <c:v>12.362005749335861</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.2137158419711671</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0454080911921671E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.2868689737640837</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2618,13 +2568,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.2741482812382703</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.588235294117601</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>15.862383575355899</c:v>
+                  <c:v>1.465041189232853</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9411764705882226</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.4062176598210829</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2705,13 +2655,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.5255489874950703</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.5882352941174</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>15.113784281612499</c:v>
+                  <c:v>1.2570969409708528</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9411764705881667</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.1982734115590272</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2960,13 +2910,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.2523055817629301</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.588235294117499</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>15.8405408758805</c:v>
+                  <c:v>1.458973772711925</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9411764705881942</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.4001502433001392</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3047,13 +2997,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.08647852728331</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.588235294117499</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>15.6747138214008</c:v>
+                  <c:v>1.4129107020231417</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9411764705881942</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.354087172611333</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3576,16 +3526,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>5.3140870128794697</c:v>
+                  <c:v>1.4761352813554083</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.2741482812381397</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10.588235294117499</c:v>
+                  <c:v>1.4650411892328166</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.9411764705881942</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3663,16 +3613,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>6.0626863066223198</c:v>
+                  <c:v>1.684079529617311</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.52554898749539</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10.5882352941174</c:v>
+                  <c:v>1.2570969409709416</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.9411764705881667</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3918,16 +3868,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>5.3359297123548002</c:v>
+                  <c:v>1.4822026978763334</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.2523055817628297</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10.588235294117499</c:v>
+                  <c:v>1.4589737727118972</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.9411764705881942</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4005,16 +3955,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>5.50175676683443</c:v>
+                  <c:v>1.5282657685651195</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.0864785272832798</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10.588235294117499</c:v>
+                  <c:v>1.4129107020231333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.9411764705881942</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6926,1329 +6876,1297 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:15" ht="16" customHeight="1">
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="3"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="33"/>
     </row>
     <row r="4" spans="2:15">
-      <c r="B4" s="58"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="27" t="s">
+      <c r="B4" s="31"/>
+      <c r="D4" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="28" t="s">
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="4"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="36"/>
     </row>
     <row r="5" spans="2:15">
-      <c r="B5" s="58"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="29" t="s">
+      <c r="B5" s="31"/>
+      <c r="D5" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="29" t="s">
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="N5" s="30"/>
-      <c r="O5" s="5"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="N5" s="38"/>
+      <c r="O5" s="39"/>
     </row>
     <row r="6" spans="2:15">
-      <c r="B6" s="58"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="31" t="s">
+      <c r="B6" s="31"/>
+      <c r="D6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="F6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="35" t="s">
+      <c r="I6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="J6" s="37" t="s">
+      <c r="J6" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="K6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="38" t="s">
+      <c r="L6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="L6" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="M6" s="40" t="s">
+      <c r="M6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="N6" s="41" t="s">
+      <c r="O6" s="12" t="s">
         <v>5</v>
-      </c>
-      <c r="O6" s="16" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="7" spans="2:15">
-      <c r="B7" s="58"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="6">
+      <c r="B7" s="31"/>
+      <c r="D7" s="2">
         <v>72.41</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="3">
         <v>1.1200000000000001</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="4">
         <v>2.11</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="6">
+      <c r="G7" s="5"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="2">
         <v>47.71</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="8">
         <v>1.25</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="9">
         <v>5.9</v>
       </c>
-      <c r="M7" s="14"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="16"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="12"/>
     </row>
     <row r="8" spans="2:15">
-      <c r="B8" s="58"/>
-      <c r="C8" s="42">
+      <c r="B8" s="31"/>
+      <c r="C8" s="22">
         <v>0</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="19">
         <v>1.44885515176778E-3</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="14">
         <v>0.22375080428647301</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="15">
         <v>7.8070939486223095E-2</v>
       </c>
-      <c r="G8" s="25">
-        <v>2.37018897866868E-3</v>
-      </c>
-      <c r="H8" s="21">
-        <v>10.3404941946124</v>
-      </c>
-      <c r="I8" s="22">
-        <v>10.44759412088</v>
-      </c>
-      <c r="J8" s="24">
+      <c r="G8" s="20">
+        <v>6.5838582740796662E-4</v>
+      </c>
+      <c r="H8" s="16">
+        <v>2.8723594985034446</v>
+      </c>
+      <c r="I8" s="17">
+        <v>2.9021094780222221</v>
+      </c>
+      <c r="J8" s="19">
         <v>2.1356775571026699E-3</v>
       </c>
-      <c r="K8" s="18">
+      <c r="K8" s="14">
         <v>0.87855217538665098</v>
       </c>
-      <c r="L8" s="19">
+      <c r="L8" s="15">
         <v>4.3141927220493703E-2</v>
       </c>
-      <c r="M8" s="25">
-        <v>5.4188553485715503E-3</v>
-      </c>
-      <c r="N8" s="21">
-        <v>10.5078106269934</v>
-      </c>
-      <c r="O8" s="22">
-        <v>10.4891174175008</v>
+      <c r="M8" s="20">
+        <v>1.5052375968254306E-3</v>
+      </c>
+      <c r="N8" s="16">
+        <v>2.9188362852759444</v>
+      </c>
+      <c r="O8" s="17">
+        <v>2.9136437270835556</v>
       </c>
     </row>
     <row r="9" spans="2:15">
-      <c r="B9" s="58"/>
-      <c r="C9" s="50">
+      <c r="B9" s="31"/>
+      <c r="C9" s="23">
         <f>128/4</f>
         <v>32</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="19">
         <v>1.1388490350476899E-3</v>
       </c>
-      <c r="E9" s="44">
+      <c r="E9" s="14">
         <v>7.7995786830834497</v>
       </c>
-      <c r="F9" s="45">
+      <c r="F9" s="15">
         <v>2.4264345007117698</v>
       </c>
-      <c r="G9" s="46">
-        <v>1.8092149471139499E-3</v>
-      </c>
-      <c r="H9" s="47">
-        <v>7.5705944386300699</v>
-      </c>
-      <c r="I9" s="48">
-        <v>5.5559626046150203</v>
-      </c>
-      <c r="J9" s="43">
+      <c r="G9" s="20">
+        <v>5.0255970753165281E-4</v>
+      </c>
+      <c r="H9" s="16">
+        <v>2.1029428996194639</v>
+      </c>
+      <c r="I9" s="17">
+        <v>1.5433229457263946</v>
+      </c>
+      <c r="J9" s="19">
         <v>9.6982174171812898E-3</v>
       </c>
-      <c r="K9" s="44">
+      <c r="K9" s="14">
         <v>13.843399756547599</v>
       </c>
-      <c r="L9" s="45">
+      <c r="L9" s="15">
         <v>0.64872937628609495</v>
       </c>
-      <c r="M9" s="46">
-        <v>3.11298841281524E-3</v>
-      </c>
-      <c r="N9" s="47">
-        <v>19.0731910385202</v>
-      </c>
-      <c r="O9" s="49">
-        <v>5.7603419265328597</v>
+      <c r="M9" s="20">
+        <v>8.6471900355978898E-4</v>
+      </c>
+      <c r="N9" s="16">
+        <v>5.2981086218111662</v>
+      </c>
+      <c r="O9" s="17">
+        <v>1.6000949795924611</v>
       </c>
     </row>
     <row r="10" spans="2:15">
-      <c r="B10" s="58"/>
-      <c r="C10" s="42">
+      <c r="B10" s="31"/>
+      <c r="C10" s="22">
         <v>63.46752</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="19">
         <v>1.4008800735708299E-3</v>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="14">
         <v>0.17171667705017499</v>
       </c>
-      <c r="F10" s="45">
+      <c r="F10" s="15">
         <v>5.1854175299510197E-2</v>
       </c>
-      <c r="G10" s="46">
-        <v>2.3994632890405802E-3</v>
-      </c>
-      <c r="H10" s="47">
-        <v>0.34143690664391402</v>
-      </c>
-      <c r="I10" s="48">
-        <v>0.18639265678729799</v>
-      </c>
-      <c r="J10" s="43">
+      <c r="G10" s="20">
+        <v>6.6651758028905004E-4</v>
+      </c>
+      <c r="H10" s="16">
+        <v>9.4843585178865E-2</v>
+      </c>
+      <c r="I10" s="17">
+        <v>5.1775737996471671E-2</v>
+      </c>
+      <c r="J10" s="19">
         <v>2.1410529642094701E-3</v>
       </c>
-      <c r="K10" s="44">
+      <c r="K10" s="14">
         <v>0.69115345903674297</v>
       </c>
-      <c r="L10" s="45">
+      <c r="L10" s="15">
         <v>4.1045338623689802E-2</v>
       </c>
-      <c r="M10" s="46">
-        <v>5.4384902206266001E-3</v>
-      </c>
-      <c r="N10" s="47">
-        <v>0.30237016814676199</v>
-      </c>
-      <c r="O10" s="49">
-        <v>0.12753018345964701</v>
+      <c r="M10" s="20">
+        <v>1.5106917279518333E-3</v>
+      </c>
+      <c r="N10" s="16">
+        <v>8.3991713374100552E-2</v>
+      </c>
+      <c r="O10" s="17">
+        <v>3.542505096101306E-2</v>
       </c>
     </row>
     <row r="11" spans="2:15" ht="16" customHeight="1">
-      <c r="B11" s="58"/>
-      <c r="C11" s="23">
+      <c r="B11" s="31"/>
+      <c r="C11" s="18">
         <f>128*0.75</f>
         <v>96</v>
       </c>
-      <c r="D11" s="51">
+      <c r="D11" s="24">
         <v>1.1388490350498701E-3</v>
       </c>
-      <c r="E11" s="52">
+      <c r="E11" s="25">
         <v>7.7995786830841096</v>
       </c>
-      <c r="F11" s="53">
+      <c r="F11" s="26">
         <v>2.4264345007119701</v>
       </c>
-      <c r="G11" s="54">
-        <v>1.8092149471130301E-3</v>
-      </c>
-      <c r="H11" s="55">
-        <v>5.8215009227073198</v>
-      </c>
-      <c r="I11" s="56">
-        <v>5.3575120040090303</v>
-      </c>
-      <c r="J11" s="51">
+      <c r="G11" s="20">
+        <v>5.0255970753139726E-4</v>
+      </c>
+      <c r="H11" s="16">
+        <v>1.6170835896409224</v>
+      </c>
+      <c r="I11" s="17">
+        <v>1.4881977788913974</v>
+      </c>
+      <c r="J11" s="24">
         <v>9.6982174171878696E-3</v>
       </c>
-      <c r="K11" s="52">
+      <c r="K11" s="25">
         <v>13.8433997565465</v>
       </c>
-      <c r="L11" s="53">
+      <c r="L11" s="26">
         <v>0.64872937628600502</v>
       </c>
-      <c r="M11" s="54">
-        <v>3.1129884128144698E-3</v>
-      </c>
-      <c r="N11" s="55">
-        <v>9.6702242405897199</v>
-      </c>
-      <c r="O11" s="57">
-        <v>4.83835550680742</v>
+      <c r="M11" s="20">
+        <v>8.6471900355957496E-4</v>
+      </c>
+      <c r="N11" s="16">
+        <v>2.6861734001638111</v>
+      </c>
+      <c r="O11" s="17">
+        <v>1.3439876407798388</v>
       </c>
     </row>
     <row r="40" spans="2:15">
-      <c r="B40" s="58" t="s">
+      <c r="B40" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
-      <c r="N40" s="2"/>
-      <c r="O40" s="3"/>
+      <c r="D40" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32"/>
+      <c r="N40" s="32"/>
+      <c r="O40" s="33"/>
     </row>
     <row r="41" spans="2:15">
-      <c r="B41" s="58"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="27" t="s">
+      <c r="B41" s="31"/>
+      <c r="D41" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="28" t="s">
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="K41" s="28"/>
-      <c r="L41" s="28"/>
-      <c r="M41" s="28"/>
-      <c r="N41" s="28"/>
-      <c r="O41" s="4"/>
+      <c r="K41" s="35"/>
+      <c r="L41" s="35"/>
+      <c r="M41" s="35"/>
+      <c r="N41" s="35"/>
+      <c r="O41" s="36"/>
     </row>
     <row r="42" spans="2:15">
-      <c r="B42" s="58"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="29" t="s">
+      <c r="B42" s="31"/>
+      <c r="D42" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
-      <c r="G42" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="29" t="s">
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" s="38"/>
+      <c r="I42" s="38"/>
+      <c r="J42" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="K42" s="29"/>
-      <c r="L42" s="29"/>
-      <c r="M42" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="N42" s="30"/>
-      <c r="O42" s="5"/>
+      <c r="K42" s="37"/>
+      <c r="L42" s="37"/>
+      <c r="M42" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="N42" s="38"/>
+      <c r="O42" s="39"/>
     </row>
     <row r="43" spans="2:15">
-      <c r="B43" s="58"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="31" t="s">
+      <c r="B43" s="31"/>
+      <c r="D43" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E43" s="32" t="s">
+      <c r="F43" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F43" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="G43" s="34" t="s">
+      <c r="G43" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H43" s="35" t="s">
+      <c r="I43" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I43" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="J43" s="37" t="s">
+      <c r="J43" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="K43" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="38" t="s">
+      <c r="L43" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="M43" s="40" t="s">
+      <c r="M43" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="N43" s="41" t="s">
+      <c r="O43" s="12" t="s">
         <v>5</v>
-      </c>
-      <c r="O43" s="16" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="44" spans="2:15">
-      <c r="B44" s="58"/>
-      <c r="C44" s="26"/>
-      <c r="D44" s="6">
+      <c r="B44" s="31"/>
+      <c r="D44" s="2">
         <v>23.6</v>
       </c>
-      <c r="E44" s="7">
+      <c r="E44" s="3">
         <v>0.16700000000000001</v>
       </c>
-      <c r="F44" s="8">
+      <c r="F44" s="4">
         <v>1.3</v>
       </c>
-      <c r="G44" s="9"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="6">
+      <c r="G44" s="5"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="2">
         <v>24.7</v>
       </c>
-      <c r="K44" s="12">
+      <c r="K44" s="8">
         <v>5.84</v>
       </c>
-      <c r="L44" s="13">
+      <c r="L44" s="9">
         <v>17.899999999999999</v>
       </c>
-      <c r="M44" s="14"/>
-      <c r="N44" s="15"/>
-      <c r="O44" s="16"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="12"/>
     </row>
     <row r="45" spans="2:15">
-      <c r="B45" s="58"/>
-      <c r="C45" s="42">
+      <c r="B45" s="31"/>
+      <c r="C45" s="22">
         <v>0</v>
       </c>
-      <c r="D45" s="17">
+      <c r="D45" s="13">
         <v>2.93662283017454E-6</v>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="14">
         <v>4.4137590820029304</v>
       </c>
-      <c r="F45" s="19">
+      <c r="F45" s="15">
         <v>8.4675504624575695E-2</v>
       </c>
-      <c r="G45" s="25">
-        <v>1.8541323033008899E-3</v>
-      </c>
-      <c r="H45" s="61">
-        <v>45.355199088398699</v>
-      </c>
-      <c r="I45" s="61">
-        <v>44.615174853890998</v>
-      </c>
-      <c r="J45" s="24">
+      <c r="G45" s="20">
+        <v>5.150367509169139E-4</v>
+      </c>
+      <c r="H45" s="16">
+        <v>12.598666413444082</v>
+      </c>
+      <c r="I45" s="17">
+        <v>12.393104126080832</v>
+      </c>
+      <c r="J45" s="19">
         <v>3.0492035439346301E-4</v>
       </c>
-      <c r="K45" s="18">
+      <c r="K45" s="14">
         <v>1.0676650890952</v>
       </c>
-      <c r="L45" s="19">
+      <c r="L45" s="15">
         <v>0.14618327284202001</v>
       </c>
-      <c r="M45" s="25">
-        <v>3.7210161523077699E-3</v>
-      </c>
-      <c r="N45" s="61">
-        <v>43.985608516044401</v>
-      </c>
-      <c r="O45" s="61">
-        <v>44.503220697609102</v>
+      <c r="M45" s="20">
+        <v>1.0336155978632694E-3</v>
+      </c>
+      <c r="N45" s="16">
+        <v>12.218224587790111</v>
+      </c>
+      <c r="O45" s="17">
+        <v>12.362005749335861</v>
       </c>
     </row>
     <row r="46" spans="2:15">
-      <c r="B46" s="58"/>
-      <c r="C46" s="50">
+      <c r="B46" s="31"/>
+      <c r="C46" s="23">
         <f>128/4</f>
         <v>32</v>
       </c>
-      <c r="D46" s="17">
+      <c r="D46" s="13">
         <v>2.4079761876719798E-6</v>
       </c>
-      <c r="E46" s="61">
+      <c r="E46" s="29">
         <v>43.457002373813403</v>
       </c>
-      <c r="F46" s="19">
+      <c r="F46" s="15">
         <v>2.23109120592928</v>
       </c>
-      <c r="G46" s="25">
-        <v>1.85467846483377E-3</v>
-      </c>
-      <c r="H46" s="61">
-        <v>50.584452310884402</v>
-      </c>
-      <c r="I46" s="61">
-        <v>20.1586062443568</v>
-      </c>
-      <c r="J46" s="24">
+      <c r="G46" s="20">
+        <v>5.1518846245382499E-4</v>
+      </c>
+      <c r="H46" s="16">
+        <v>14.051236753023444</v>
+      </c>
+      <c r="I46" s="17">
+        <v>5.5996128456546668</v>
+      </c>
+      <c r="J46" s="19">
         <v>2.9101210966995497E-4</v>
       </c>
-      <c r="K46" s="61">
+      <c r="K46" s="29">
         <v>35.240304495168701</v>
       </c>
-      <c r="L46" s="19">
+      <c r="L46" s="15">
         <v>10.965128920599399</v>
       </c>
-      <c r="M46" s="25">
-        <v>3.7290506812936502E-3</v>
-      </c>
-      <c r="N46" s="61">
-        <v>38.653362881352599</v>
-      </c>
-      <c r="O46" s="61">
-        <v>25.969377031096201</v>
+      <c r="M46" s="20">
+        <v>1.0358474114704583E-3</v>
+      </c>
+      <c r="N46" s="16">
+        <v>10.737045244820166</v>
+      </c>
+      <c r="O46" s="17">
+        <v>7.2137158419711671</v>
       </c>
     </row>
     <row r="47" spans="2:15">
-      <c r="B47" s="58"/>
-      <c r="C47" s="42">
+      <c r="B47" s="31"/>
+      <c r="C47" s="22">
         <v>63.46752</v>
       </c>
-      <c r="D47" s="17">
+      <c r="D47" s="13">
         <v>2.96104890834469E-6</v>
       </c>
-      <c r="E47" s="18">
+      <c r="E47" s="14">
         <v>0.27176022159733798</v>
       </c>
-      <c r="F47" s="19">
+      <c r="F47" s="15">
         <v>4.2780739562193202E-3</v>
       </c>
-      <c r="G47" s="25">
-        <v>1.8541412299733801E-3</v>
-      </c>
-      <c r="H47" s="21">
-        <v>3.2044600007555699E-2</v>
-      </c>
-      <c r="I47" s="22">
-        <v>2.3091910388783402E-2</v>
-      </c>
-      <c r="J47" s="24">
+      <c r="G47" s="20">
+        <v>5.1503923054816109E-4</v>
+      </c>
+      <c r="H47" s="16">
+        <v>8.9012777798765826E-3</v>
+      </c>
+      <c r="I47" s="17">
+        <v>6.4144195524398337E-3</v>
+      </c>
+      <c r="J47" s="19">
         <v>3.0527900397714299E-4</v>
       </c>
-      <c r="K47" s="18">
+      <c r="K47" s="14">
         <v>7.2079676448087396E-2</v>
       </c>
-      <c r="L47" s="19">
+      <c r="L47" s="15">
         <v>1.03760284992311E-2</v>
       </c>
-      <c r="M47" s="25">
-        <v>3.72122733483028E-3</v>
-      </c>
-      <c r="N47" s="21">
-        <v>7.4304893485778803E-2</v>
-      </c>
-      <c r="O47" s="22">
-        <v>2.8963469128291799E-2</v>
+      <c r="M47" s="20">
+        <v>1.0336742596750779E-3</v>
+      </c>
+      <c r="N47" s="16">
+        <v>2.064024819049411E-2</v>
+      </c>
+      <c r="O47" s="17">
+        <v>8.0454080911921671E-3</v>
       </c>
     </row>
     <row r="48" spans="2:15">
-      <c r="B48" s="58"/>
-      <c r="C48" s="23">
+      <c r="B48" s="31"/>
+      <c r="C48" s="18">
         <f>128*0.75</f>
         <v>96</v>
       </c>
-      <c r="D48" s="17">
+      <c r="D48" s="13">
         <v>2.4079761907031999E-6</v>
       </c>
-      <c r="E48" s="61">
+      <c r="E48" s="29">
         <v>43.457002373812998</v>
       </c>
-      <c r="F48" s="19">
+      <c r="F48" s="15">
         <v>2.23109120592843</v>
       </c>
-      <c r="G48" s="25">
-        <v>1.85467846481108E-3</v>
-      </c>
-      <c r="H48" s="61">
-        <v>95.340692448022693</v>
-      </c>
-      <c r="I48" s="61">
-        <v>24.848705492333298</v>
-      </c>
-      <c r="J48" s="24">
+      <c r="G48" s="20">
+        <v>5.1518846244752231E-4</v>
+      </c>
+      <c r="H48" s="29">
+        <v>26.483525680006302</v>
+      </c>
+      <c r="I48" s="17">
+        <v>6.9024181923148049</v>
+      </c>
+      <c r="J48" s="19">
         <v>2.9101210964869502E-4</v>
       </c>
-      <c r="K48" s="60">
+      <c r="K48" s="28">
         <v>35.2403044951688</v>
       </c>
-      <c r="L48" s="19">
+      <c r="L48" s="15">
         <v>10.965128920599399</v>
       </c>
-      <c r="M48" s="25">
-        <v>3.729050681316E-3</v>
-      </c>
-      <c r="N48" s="21">
-        <v>6.5130388260926697</v>
-      </c>
-      <c r="O48" s="61">
-        <v>19.032728305550702</v>
+      <c r="M48" s="20">
+        <v>1.0358474114766667E-3</v>
+      </c>
+      <c r="N48" s="16">
+        <v>1.8091774516924082</v>
+      </c>
+      <c r="O48" s="17">
+        <v>5.2868689737640837</v>
       </c>
     </row>
     <row r="51" spans="3:14">
-      <c r="C51" s="59"/>
+      <c r="C51" s="27"/>
     </row>
     <row r="53" spans="3:14">
       <c r="N53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="3:14">
-      <c r="D54" s="59"/>
+      <c r="D54" s="27"/>
     </row>
     <row r="58" spans="3:14">
-      <c r="D58" s="59"/>
+      <c r="D58" s="27"/>
     </row>
     <row r="80" spans="2:15">
-      <c r="B80" s="58" t="s">
-        <v>13</v>
+      <c r="B80" s="31" t="s">
+        <v>12</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-      <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
-      <c r="N80" s="2"/>
-      <c r="O80" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="D80" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="32"/>
+      <c r="F80" s="32"/>
+      <c r="G80" s="32"/>
+      <c r="H80" s="32"/>
+      <c r="I80" s="32"/>
+      <c r="J80" s="32"/>
+      <c r="K80" s="32"/>
+      <c r="L80" s="32"/>
+      <c r="M80" s="32"/>
+      <c r="N80" s="32"/>
+      <c r="O80" s="33"/>
     </row>
     <row r="81" spans="2:15">
-      <c r="B81" s="58"/>
-      <c r="C81" s="26"/>
-      <c r="D81" s="27" t="s">
+      <c r="B81" s="31"/>
+      <c r="D81" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="E81" s="27"/>
-      <c r="F81" s="27"/>
-      <c r="G81" s="27"/>
-      <c r="H81" s="27"/>
-      <c r="I81" s="27"/>
-      <c r="J81" s="28" t="s">
+      <c r="E81" s="34"/>
+      <c r="F81" s="34"/>
+      <c r="G81" s="34"/>
+      <c r="H81" s="34"/>
+      <c r="I81" s="34"/>
+      <c r="J81" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="K81" s="28"/>
-      <c r="L81" s="28"/>
-      <c r="M81" s="28"/>
-      <c r="N81" s="28"/>
-      <c r="O81" s="4"/>
+      <c r="K81" s="35"/>
+      <c r="L81" s="35"/>
+      <c r="M81" s="35"/>
+      <c r="N81" s="35"/>
+      <c r="O81" s="36"/>
     </row>
     <row r="82" spans="2:15">
-      <c r="B82" s="58"/>
-      <c r="C82" s="26"/>
-      <c r="D82" s="29" t="s">
+      <c r="B82" s="31"/>
+      <c r="D82" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E82" s="29"/>
-      <c r="F82" s="29"/>
-      <c r="G82" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="H82" s="30"/>
-      <c r="I82" s="30"/>
-      <c r="J82" s="29" t="s">
+      <c r="E82" s="37"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="H82" s="38"/>
+      <c r="I82" s="38"/>
+      <c r="J82" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="K82" s="29"/>
-      <c r="L82" s="29"/>
-      <c r="M82" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="N82" s="30"/>
-      <c r="O82" s="5"/>
+      <c r="K82" s="37"/>
+      <c r="L82" s="37"/>
+      <c r="M82" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="N82" s="38"/>
+      <c r="O82" s="39"/>
     </row>
     <row r="83" spans="2:15">
-      <c r="B83" s="58"/>
-      <c r="C83" s="26"/>
-      <c r="D83" s="31" t="s">
+      <c r="B83" s="31"/>
+      <c r="D83" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E83" s="32" t="s">
+      <c r="F83" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F83" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="G83" s="34" t="s">
+      <c r="G83" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H83" s="35" t="s">
+      <c r="I83" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I83" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="J83" s="37" t="s">
+      <c r="J83" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="38" t="s">
+      <c r="L83" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="L83" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="M83" s="40" t="s">
+      <c r="M83" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="N83" s="41" t="s">
+      <c r="O83" s="12" t="s">
         <v>5</v>
-      </c>
-      <c r="O83" s="16" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="84" spans="2:15">
-      <c r="B84" s="58"/>
-      <c r="C84" s="26"/>
-      <c r="D84" s="6">
+      <c r="B84" s="31"/>
+      <c r="D84" s="2">
         <f>100/SQRT(2)</f>
         <v>70.710678118654741</v>
       </c>
-      <c r="E84" s="7">
+      <c r="E84" s="3">
         <f>50/SQRT(2)</f>
         <v>35.35533905932737</v>
       </c>
-      <c r="F84" s="8">
+      <c r="F84" s="4">
         <f>10/SQRT(2)</f>
         <v>7.0710678118654746</v>
       </c>
-      <c r="G84" s="9"/>
-      <c r="H84" s="10"/>
-      <c r="I84" s="11"/>
-      <c r="J84" s="6">
+      <c r="G84" s="5"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="7"/>
+      <c r="J84" s="2">
         <f>50/SQRT(2)</f>
         <v>35.35533905932737</v>
       </c>
-      <c r="K84" s="7">
+      <c r="K84" s="3">
         <f>10/SQRT(2)</f>
         <v>7.0710678118654746</v>
       </c>
-      <c r="L84" s="13">
+      <c r="L84" s="9">
         <f>5/SQRT(2)</f>
         <v>3.5355339059327373</v>
       </c>
-      <c r="M84" s="14"/>
-      <c r="N84" s="15"/>
-      <c r="O84" s="16"/>
+      <c r="M84" s="10"/>
+      <c r="N84" s="11"/>
+      <c r="O84" s="12"/>
     </row>
     <row r="85" spans="2:15">
-      <c r="B85" s="58"/>
-      <c r="C85" s="42">
+      <c r="B85" s="31"/>
+      <c r="C85" s="22">
         <v>0</v>
       </c>
-      <c r="D85" s="17">
+      <c r="D85" s="13">
         <v>0</v>
       </c>
-      <c r="E85" s="18">
+      <c r="E85" s="14">
         <v>0</v>
       </c>
-      <c r="F85" s="19">
+      <c r="F85" s="15">
         <v>0</v>
       </c>
-      <c r="G85" s="25">
+      <c r="G85" s="20">
         <v>0</v>
       </c>
-      <c r="H85" s="21">
+      <c r="H85" s="16">
         <v>0</v>
       </c>
-      <c r="I85" s="22">
+      <c r="I85" s="17">
         <v>0</v>
       </c>
-      <c r="J85" s="24">
+      <c r="J85" s="19">
         <v>0</v>
       </c>
-      <c r="K85" s="18">
+      <c r="K85" s="14">
         <v>0</v>
       </c>
-      <c r="L85" s="19">
+      <c r="L85" s="15">
         <v>0</v>
       </c>
-      <c r="M85" s="25">
+      <c r="M85" s="20">
         <v>0</v>
       </c>
-      <c r="N85" s="21">
+      <c r="N85" s="16">
         <v>0</v>
       </c>
-      <c r="O85" s="22">
+      <c r="O85" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="2:15">
-      <c r="B86" s="58"/>
-      <c r="C86" s="50">
+      <c r="B86" s="31"/>
+      <c r="C86" s="23">
         <f>128/4</f>
         <v>32</v>
       </c>
-      <c r="D86" s="17">
+      <c r="D86" s="13">
         <v>6.0291550413456805E-14</v>
       </c>
-      <c r="E86" s="18">
+      <c r="E86" s="14">
         <v>0.95937493032495502</v>
       </c>
-      <c r="F86" s="19">
+      <c r="F86" s="15">
         <v>43.762350279568999</v>
       </c>
       <c r="G86" s="20">
-        <v>1.7334912947691101E-13</v>
-      </c>
-      <c r="H86" s="21">
-        <v>5.2741482812382703</v>
-      </c>
-      <c r="I86" s="22">
-        <v>4.5255489874950703</v>
-      </c>
-      <c r="J86" s="17">
+        <v>4.815253596580861E-14</v>
+      </c>
+      <c r="H86" s="16">
+        <v>1.465041189232853</v>
+      </c>
+      <c r="I86" s="17">
+        <v>1.2570969409708528</v>
+      </c>
+      <c r="J86" s="13">
         <v>5.2252677024996E-14</v>
       </c>
-      <c r="K86" s="18">
+      <c r="K86" s="14">
         <v>2.61173734662444</v>
       </c>
-      <c r="L86" s="19">
+      <c r="L86" s="15">
         <v>14.0038956314889</v>
       </c>
       <c r="M86" s="20">
-        <v>1.4850173190112699E-13</v>
-      </c>
-      <c r="N86" s="21">
-        <v>5.2523055817629301</v>
-      </c>
-      <c r="O86" s="22">
-        <v>5.08647852728331</v>
+        <v>4.1250481083646383E-14</v>
+      </c>
+      <c r="N86" s="16">
+        <v>1.458973772711925</v>
+      </c>
+      <c r="O86" s="17">
+        <v>1.4129107020231417</v>
       </c>
     </row>
     <row r="87" spans="2:15">
-      <c r="B87" s="58"/>
-      <c r="C87" s="42">
+      <c r="B87" s="31"/>
+      <c r="C87" s="22">
         <v>64</v>
       </c>
-      <c r="D87" s="17">
+      <c r="D87" s="13">
         <v>2.81360568596132E-14</v>
       </c>
-      <c r="E87" s="60">
+      <c r="E87" s="28">
         <v>6.43109871076886E-14</v>
       </c>
-      <c r="F87" s="62">
+      <c r="F87" s="30">
         <v>5.5518469339051202E-13</v>
       </c>
       <c r="G87" s="20">
-        <v>2.3779308166185599E-14</v>
-      </c>
-      <c r="H87" s="21">
-        <v>10.588235294117601</v>
-      </c>
-      <c r="I87" s="22">
-        <v>10.5882352941174</v>
-      </c>
-      <c r="J87" s="17">
+        <v>6.6053633794959998E-15</v>
+      </c>
+      <c r="H87" s="16">
+        <v>2.9411764705882226</v>
+      </c>
+      <c r="I87" s="17">
+        <v>2.9411764705881667</v>
+      </c>
+      <c r="J87" s="13">
         <v>3.0145775206728403E-14</v>
       </c>
-      <c r="K87" s="60">
+      <c r="K87" s="28">
         <v>1.29375618595543E-13</v>
       </c>
-      <c r="L87" s="62">
+      <c r="L87" s="30">
         <v>3.7179789421631099E-13</v>
       </c>
       <c r="M87" s="20">
-        <v>1.79754673591127E-14</v>
-      </c>
-      <c r="N87" s="21">
-        <v>10.588235294117499</v>
-      </c>
-      <c r="O87" s="22">
-        <v>10.588235294117499</v>
+        <v>4.9931853775313058E-15</v>
+      </c>
+      <c r="N87" s="16">
+        <v>2.9411764705881942</v>
+      </c>
+      <c r="O87" s="17">
+        <v>2.9411764705881942</v>
       </c>
     </row>
     <row r="88" spans="2:15">
-      <c r="B88" s="58"/>
-      <c r="C88" s="23">
+      <c r="B88" s="31"/>
+      <c r="C88" s="18">
         <f>128*0.75</f>
         <v>96</v>
       </c>
-      <c r="D88" s="17">
+      <c r="D88" s="13">
         <v>5.62721137192264E-14</v>
       </c>
-      <c r="E88" s="18">
+      <c r="E88" s="14">
         <v>0.95937493032478804</v>
       </c>
-      <c r="F88" s="19">
+      <c r="F88" s="15">
         <v>43.7623502795701</v>
       </c>
       <c r="G88" s="20">
-        <v>1.7123932515678501E-13</v>
-      </c>
-      <c r="H88" s="21">
-        <v>15.862383575355899</v>
-      </c>
-      <c r="I88" s="22">
-        <v>15.113784281612499</v>
-      </c>
-      <c r="J88" s="17">
+        <v>4.7566479210218055E-14</v>
+      </c>
+      <c r="H88" s="16">
+        <v>4.4062176598210829</v>
+      </c>
+      <c r="I88" s="17">
+        <v>4.1982734115590272</v>
+      </c>
+      <c r="J88" s="13">
         <v>6.4310987107687401E-14</v>
       </c>
-      <c r="K88" s="18">
+      <c r="K88" s="14">
         <v>2.6117373466243201</v>
       </c>
-      <c r="L88" s="19">
+      <c r="L88" s="15">
         <v>14.003895631489</v>
       </c>
       <c r="M88" s="20">
-        <v>1.5515233899300399E-13</v>
-      </c>
-      <c r="N88" s="21">
-        <v>15.8405408758805</v>
-      </c>
-      <c r="O88" s="22">
-        <v>15.6747138214008</v>
+        <v>4.3097871942501108E-14</v>
+      </c>
+      <c r="N88" s="16">
+        <v>4.4001502433001392</v>
+      </c>
+      <c r="O88" s="17">
+        <v>4.354087172611333</v>
       </c>
     </row>
     <row r="92" spans="2:15">
-      <c r="C92" s="59"/>
-      <c r="D92" s="59"/>
-      <c r="E92" s="59"/>
+      <c r="C92" s="27"/>
+      <c r="D92" s="27"/>
+      <c r="E92" s="27"/>
     </row>
     <row r="93" spans="2:15">
-      <c r="D93" s="59"/>
+      <c r="D93" s="27"/>
     </row>
     <row r="94" spans="2:15">
-      <c r="D94" s="59"/>
+      <c r="D94" s="27"/>
     </row>
     <row r="95" spans="2:15">
-      <c r="C95" s="59"/>
-      <c r="D95" s="59"/>
-      <c r="E95" s="59"/>
+      <c r="C95" s="27"/>
+      <c r="D95" s="27"/>
+      <c r="E95" s="27"/>
     </row>
     <row r="96" spans="2:15">
-      <c r="D96" s="59"/>
+      <c r="D96" s="27"/>
     </row>
     <row r="97" spans="3:5">
-      <c r="D97" s="59"/>
+      <c r="D97" s="27"/>
     </row>
     <row r="99" spans="3:5">
-      <c r="C99" s="59"/>
-      <c r="D99" s="59"/>
-      <c r="E99" s="59"/>
+      <c r="C99" s="27"/>
+      <c r="D99" s="27"/>
+      <c r="E99" s="27"/>
     </row>
     <row r="102" spans="3:5">
-      <c r="C102" s="59"/>
-      <c r="D102" s="59"/>
-      <c r="E102" s="59"/>
+      <c r="C102" s="27"/>
+      <c r="D102" s="27"/>
+      <c r="E102" s="27"/>
     </row>
     <row r="118" spans="2:15">
-      <c r="B118" s="58" t="s">
-        <v>14</v>
+      <c r="B118" s="31" t="s">
+        <v>13</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-      <c r="H118" s="2"/>
-      <c r="I118" s="2"/>
-      <c r="J118" s="2"/>
-      <c r="K118" s="2"/>
-      <c r="L118" s="2"/>
-      <c r="M118" s="2"/>
-      <c r="N118" s="2"/>
-      <c r="O118" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="D118" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" s="32"/>
+      <c r="F118" s="32"/>
+      <c r="G118" s="32"/>
+      <c r="H118" s="32"/>
+      <c r="I118" s="32"/>
+      <c r="J118" s="32"/>
+      <c r="K118" s="32"/>
+      <c r="L118" s="32"/>
+      <c r="M118" s="32"/>
+      <c r="N118" s="32"/>
+      <c r="O118" s="33"/>
     </row>
     <row r="119" spans="2:15">
-      <c r="B119" s="58"/>
-      <c r="C119" s="26"/>
-      <c r="D119" s="27" t="s">
+      <c r="B119" s="31"/>
+      <c r="D119" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="E119" s="27"/>
-      <c r="F119" s="27"/>
-      <c r="G119" s="27"/>
-      <c r="H119" s="27"/>
-      <c r="I119" s="27"/>
-      <c r="J119" s="28" t="s">
+      <c r="E119" s="34"/>
+      <c r="F119" s="34"/>
+      <c r="G119" s="34"/>
+      <c r="H119" s="34"/>
+      <c r="I119" s="34"/>
+      <c r="J119" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="K119" s="28"/>
-      <c r="L119" s="28"/>
-      <c r="M119" s="28"/>
-      <c r="N119" s="28"/>
-      <c r="O119" s="4"/>
+      <c r="K119" s="35"/>
+      <c r="L119" s="35"/>
+      <c r="M119" s="35"/>
+      <c r="N119" s="35"/>
+      <c r="O119" s="36"/>
     </row>
     <row r="120" spans="2:15">
-      <c r="B120" s="58"/>
-      <c r="C120" s="26"/>
-      <c r="D120" s="29" t="s">
+      <c r="B120" s="31"/>
+      <c r="D120" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E120" s="29"/>
-      <c r="F120" s="29"/>
-      <c r="G120" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="H120" s="30"/>
-      <c r="I120" s="30"/>
-      <c r="J120" s="29" t="s">
+      <c r="E120" s="37"/>
+      <c r="F120" s="37"/>
+      <c r="G120" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="H120" s="38"/>
+      <c r="I120" s="38"/>
+      <c r="J120" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="K120" s="29"/>
-      <c r="L120" s="29"/>
-      <c r="M120" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="N120" s="30"/>
-      <c r="O120" s="5"/>
+      <c r="K120" s="37"/>
+      <c r="L120" s="37"/>
+      <c r="M120" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="N120" s="38"/>
+      <c r="O120" s="39"/>
     </row>
     <row r="121" spans="2:15">
-      <c r="B121" s="58"/>
-      <c r="C121" s="26"/>
-      <c r="D121" s="31" t="s">
+      <c r="B121" s="31"/>
+      <c r="D121" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E121" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E121" s="32" t="s">
+      <c r="F121" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F121" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="G121" s="34" t="s">
+      <c r="G121" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H121" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H121" s="35" t="s">
+      <c r="I121" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I121" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="J121" s="37" t="s">
+      <c r="J121" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="K121" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K121" s="38" t="s">
+      <c r="L121" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="L121" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="M121" s="40" t="s">
+      <c r="M121" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N121" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="N121" s="41" t="s">
+      <c r="O121" s="12" t="s">
         <v>5</v>
-      </c>
-      <c r="O121" s="16" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="122" spans="2:15">
-      <c r="B122" s="58"/>
-      <c r="C122" s="26"/>
-      <c r="D122" s="6">
+      <c r="B122" s="31"/>
+      <c r="D122" s="2">
         <f>100/SQRT(2)</f>
         <v>70.710678118654741</v>
       </c>
-      <c r="E122" s="7">
+      <c r="E122" s="3">
         <f>50/SQRT(2)</f>
         <v>35.35533905932737</v>
       </c>
-      <c r="F122" s="8">
+      <c r="F122" s="4">
         <f>10/SQRT(2)</f>
         <v>7.0710678118654746</v>
       </c>
-      <c r="G122" s="9"/>
-      <c r="H122" s="10"/>
-      <c r="I122" s="11"/>
-      <c r="J122" s="6">
+      <c r="G122" s="5"/>
+      <c r="H122" s="6"/>
+      <c r="I122" s="7"/>
+      <c r="J122" s="2">
         <f>50/SQRT(2)</f>
         <v>35.35533905932737</v>
       </c>
-      <c r="K122" s="7">
+      <c r="K122" s="3">
         <f>10/SQRT(2)</f>
         <v>7.0710678118654746</v>
       </c>
-      <c r="L122" s="13">
+      <c r="L122" s="9">
         <f>5/SQRT(2)</f>
         <v>3.5355339059327373</v>
       </c>
-      <c r="M122" s="14"/>
-      <c r="N122" s="15"/>
-      <c r="O122" s="16"/>
+      <c r="M122" s="10"/>
+      <c r="N122" s="11"/>
+      <c r="O122" s="12"/>
     </row>
     <row r="123" spans="2:15">
-      <c r="B123" s="58"/>
-      <c r="C123" s="42">
+      <c r="B123" s="31"/>
+      <c r="C123" s="22">
         <v>0</v>
       </c>
-      <c r="D123" s="17">
+      <c r="D123" s="13">
         <v>7.2349860496148199E-14</v>
       </c>
-      <c r="E123" s="18">
+      <c r="E123" s="14">
         <v>0.95937493032490595</v>
       </c>
-      <c r="F123" s="19">
+      <c r="F123" s="15">
         <v>43.762350279569098</v>
       </c>
       <c r="G123" s="20">
-        <v>1.6052605640701199E-13</v>
-      </c>
-      <c r="H123" s="21">
-        <v>5.3140870128794697</v>
-      </c>
-      <c r="I123" s="22">
-        <v>6.0626863066223198</v>
-      </c>
-      <c r="J123" s="17">
+        <v>4.4590571224169998E-14</v>
+      </c>
+      <c r="H123" s="16">
+        <v>1.4761352813554083</v>
+      </c>
+      <c r="I123" s="17">
+        <v>1.684079529617311</v>
+      </c>
+      <c r="J123" s="13">
         <v>5.62721137192264E-14</v>
       </c>
-      <c r="K123" s="18">
+      <c r="K123" s="14">
         <v>2.61173734662446</v>
       </c>
-      <c r="L123" s="19">
+      <c r="L123" s="15">
         <v>14.003895631488801</v>
       </c>
       <c r="M123" s="20">
-        <v>1.45756546373355E-13</v>
-      </c>
-      <c r="N123" s="21">
-        <v>5.3359297123548002</v>
-      </c>
-      <c r="O123" s="22">
-        <v>5.50175676683443</v>
+        <v>4.0487929548154168E-14</v>
+      </c>
+      <c r="N123" s="16">
+        <v>1.4822026978763334</v>
+      </c>
+      <c r="O123" s="17">
+        <v>1.5282657685651195</v>
       </c>
     </row>
     <row r="124" spans="2:15">
-      <c r="B124" s="58"/>
-      <c r="C124" s="50">
+      <c r="B124" s="31"/>
+      <c r="C124" s="23">
         <f>128/4</f>
         <v>32</v>
       </c>
-      <c r="D124" s="17">
+      <c r="D124" s="13">
         <v>0</v>
       </c>
-      <c r="E124" s="18">
+      <c r="E124" s="14">
         <v>0</v>
       </c>
-      <c r="F124" s="19">
+      <c r="F124" s="15">
         <v>0</v>
       </c>
       <c r="G124" s="20">
         <v>0</v>
       </c>
-      <c r="H124" s="21">
+      <c r="H124" s="16">
         <v>0</v>
       </c>
-      <c r="I124" s="22">
+      <c r="I124" s="17">
         <v>0</v>
       </c>
-      <c r="J124" s="17">
+      <c r="J124" s="13">
         <v>0</v>
       </c>
-      <c r="K124" s="18">
+      <c r="K124" s="14">
         <v>0</v>
       </c>
-      <c r="L124" s="19">
+      <c r="L124" s="15">
         <v>0</v>
       </c>
       <c r="M124" s="20">
         <v>0</v>
       </c>
-      <c r="N124" s="21">
+      <c r="N124" s="16">
         <v>0</v>
       </c>
-      <c r="O124" s="22">
+      <c r="O124" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="2:15">
-      <c r="B125" s="58"/>
-      <c r="C125" s="42">
+      <c r="B125" s="31"/>
+      <c r="C125" s="22">
         <v>64</v>
       </c>
-      <c r="D125" s="17">
+      <c r="D125" s="13">
         <v>6.0291550413456805E-14</v>
       </c>
-      <c r="E125" s="18">
+      <c r="E125" s="14">
         <v>0.95937493032492804</v>
       </c>
-      <c r="F125" s="19">
+      <c r="F125" s="15">
         <v>43.762350279568601</v>
       </c>
       <c r="G125" s="20">
-        <v>1.6645515716329899E-13</v>
-      </c>
-      <c r="H125" s="21">
-        <v>5.2741482812381397</v>
-      </c>
-      <c r="I125" s="22">
-        <v>4.52554898749539</v>
-      </c>
-      <c r="J125" s="17">
+        <v>4.623754365647194E-14</v>
+      </c>
+      <c r="H125" s="16">
+        <v>1.4650411892328166</v>
+      </c>
+      <c r="I125" s="17">
+        <v>1.2570969409709416</v>
+      </c>
+      <c r="J125" s="13">
         <v>5.62721137192264E-14</v>
       </c>
-      <c r="K125" s="18">
+      <c r="K125" s="14">
         <v>2.61173734662444</v>
       </c>
-      <c r="L125" s="19">
+      <c r="L125" s="15">
         <v>14.0038956314886</v>
       </c>
       <c r="M125" s="20">
-        <v>1.5410753021258099E-13</v>
-      </c>
-      <c r="N125" s="21">
-        <v>5.2523055817628297</v>
-      </c>
-      <c r="O125" s="22">
-        <v>5.0864785272832798</v>
+        <v>4.2807647281272499E-14</v>
+      </c>
+      <c r="N125" s="16">
+        <v>1.4589737727118972</v>
+      </c>
+      <c r="O125" s="17">
+        <v>1.4129107020231333</v>
       </c>
     </row>
     <row r="126" spans="2:15">
-      <c r="B126" s="58"/>
-      <c r="C126" s="23">
+      <c r="B126" s="31"/>
+      <c r="C126" s="18">
         <f>128*0.75</f>
         <v>96</v>
       </c>
-      <c r="D126" s="17">
+      <c r="D126" s="13">
         <v>2.81360568596132E-14</v>
       </c>
-      <c r="E126" s="60">
+      <c r="E126" s="28">
         <v>1.24602537521145E-13</v>
       </c>
-      <c r="F126" s="62">
+      <c r="F126" s="30">
         <v>4.30833370662789E-13</v>
       </c>
       <c r="G126" s="20">
-        <v>1.79754673591127E-14</v>
-      </c>
-      <c r="H126" s="21">
-        <v>10.588235294117499</v>
-      </c>
-      <c r="I126" s="22">
-        <v>10.5882352941174</v>
-      </c>
-      <c r="J126" s="17">
+        <v>4.9931853775313058E-15</v>
+      </c>
+      <c r="H126" s="16">
+        <v>2.9411764705881942</v>
+      </c>
+      <c r="I126" s="17">
+        <v>2.9411764705881667</v>
+      </c>
+      <c r="J126" s="13">
         <v>4.01943669423046E-14</v>
       </c>
-      <c r="K126" s="60">
+      <c r="K126" s="28">
         <v>1.45704580165855E-13</v>
       </c>
-      <c r="L126" s="62">
+      <c r="L126" s="30">
         <v>2.2358116611656499E-13</v>
       </c>
       <c r="M126" s="20">
-        <v>8.9877336795563501E-15</v>
-      </c>
-      <c r="N126" s="21">
-        <v>10.588235294117499</v>
-      </c>
-      <c r="O126" s="22">
-        <v>10.588235294117499</v>
+        <v>2.4965926887656529E-15</v>
+      </c>
+      <c r="N126" s="16">
+        <v>2.9411764705881942</v>
+      </c>
+      <c r="O126" s="17">
+        <v>2.9411764705881942</v>
       </c>
     </row>
     <row r="130" spans="4:6">
-      <c r="D130" s="59"/>
-      <c r="E130" s="59"/>
-      <c r="F130" s="59"/>
+      <c r="D130" s="27"/>
+      <c r="E130" s="27"/>
+      <c r="F130" s="27"/>
     </row>
     <row r="131" spans="4:6">
-      <c r="F131" s="59"/>
+      <c r="F131" s="27"/>
     </row>
     <row r="132" spans="4:6">
-      <c r="F132" s="59"/>
+      <c r="F132" s="27"/>
     </row>
     <row r="133" spans="4:6">
-      <c r="D133" s="59"/>
-      <c r="E133" s="59"/>
-      <c r="F133" s="59"/>
+      <c r="D133" s="27"/>
+      <c r="E133" s="27"/>
+      <c r="F133" s="27"/>
     </row>
     <row r="134" spans="4:6">
-      <c r="F134" s="59"/>
+      <c r="F134" s="27"/>
     </row>
     <row r="135" spans="4:6">
-      <c r="F135" s="59"/>
+      <c r="F135" s="27"/>
     </row>
     <row r="137" spans="4:6">
-      <c r="D137" s="59"/>
-      <c r="E137" s="59"/>
-      <c r="F137" s="59"/>
+      <c r="D137" s="27"/>
+      <c r="E137" s="27"/>
+      <c r="F137" s="27"/>
     </row>
     <row r="140" spans="4:6">
-      <c r="D140" s="59"/>
-      <c r="E140" s="59"/>
-      <c r="F140" s="59"/>
+      <c r="D140" s="27"/>
+      <c r="E140" s="27"/>
+      <c r="F140" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B118:B126"/>
-    <mergeCell ref="D118:O118"/>
-    <mergeCell ref="D119:I119"/>
-    <mergeCell ref="J119:O119"/>
-    <mergeCell ref="D120:F120"/>
-    <mergeCell ref="G120:I120"/>
-    <mergeCell ref="J120:L120"/>
-    <mergeCell ref="M120:O120"/>
-    <mergeCell ref="B80:B88"/>
-    <mergeCell ref="D80:O80"/>
-    <mergeCell ref="D81:I81"/>
-    <mergeCell ref="J81:O81"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="G82:I82"/>
-    <mergeCell ref="J82:L82"/>
-    <mergeCell ref="M82:O82"/>
     <mergeCell ref="B3:B11"/>
     <mergeCell ref="B40:B48"/>
     <mergeCell ref="D40:O40"/>
@@ -8265,6 +8183,22 @@
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="J5:L5"/>
     <mergeCell ref="M5:O5"/>
+    <mergeCell ref="B80:B88"/>
+    <mergeCell ref="D80:O80"/>
+    <mergeCell ref="D81:I81"/>
+    <mergeCell ref="J81:O81"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="G82:I82"/>
+    <mergeCell ref="J82:L82"/>
+    <mergeCell ref="M82:O82"/>
+    <mergeCell ref="B118:B126"/>
+    <mergeCell ref="D118:O118"/>
+    <mergeCell ref="D119:I119"/>
+    <mergeCell ref="J119:O119"/>
+    <mergeCell ref="D120:F120"/>
+    <mergeCell ref="G120:I120"/>
+    <mergeCell ref="J120:L120"/>
+    <mergeCell ref="M120:O120"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
